--- a/output/COHR/COHR.xlsx
+++ b/output/COHR/COHR.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,12 +83,6 @@
       <name val="Consolas"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00991B1B"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -140,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,7 +165,6 @@
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -581,7 +574,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$123</t>
+          <t>$114</t>
         </is>
       </c>
     </row>
@@ -603,7 +596,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>-65.4%</t>
+          <t>-68.0%</t>
         </is>
       </c>
     </row>
@@ -615,7 +608,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>$123</t>
+          <t>$114</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -625,7 +618,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>-65.4%</t>
+          <t>-68.0%</t>
         </is>
       </c>
     </row>
@@ -867,7 +860,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>The problem is price. At roughly 12x sales for a components maker whose datacom margins are perpetually reset each generation, an intrinsic DCF lands near $123 against a $356 stock. The franchise is real; the multiple prices a flawless decade.</t>
+          <t>The problem is price. At roughly 12x sales for a components maker whose datacom margins are perpetually reset each generation, an intrinsic DCF lands near $114 against a $356 stock. The franchise is real; the multiple prices a flawless decade.</t>
         </is>
       </c>
     </row>
@@ -1001,7 +994,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Bear gets a heavy 25% because transceiver pricing resets and a 5x run leave the stock exposed to any single soft print. Base 45% for the constructive AI-optical ramp. Bull 15% for the CPO/1.6T acceleration. Cross-check 20% anchors intrinsic value against the peer multiple.</t>
+          <t>Bear gets a heavy 25% because transceiver pricing resets and a 5x run leave the stock exposed to any single soft print. Base 45% for the constructive AI-optical ramp. Bull 10% for the CPO/1.6T acceleration. Cross-check 20% anchors intrinsic value against the peer multiple.</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1215,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>-65%</t>
+          <t>-68%</t>
         </is>
       </c>
     </row>
@@ -3662,10 +3655,10 @@
         <v>183.8</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D7" t="n">
-        <v>27.57</v>
+        <v>18.38</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
@@ -3711,13 +3704,8 @@
           <t>Weight total</t>
         </is>
       </c>
-      <c r="C10" s="25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E10" s="26" t="inlineStr">
-        <is>
-          <t>WARNING: weights do not sum to 1.0</t>
-        </is>
+      <c r="C10" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3727,7 +3715,7 @@
         </is>
       </c>
       <c r="D11" s="19" t="n">
-        <v>123.09</v>
+        <v>113.9</v>
       </c>
     </row>
     <row r="12">
@@ -3747,7 +3735,7 @@
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>-0.654</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="14"/>
@@ -3762,7 +3750,7 @@
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Bear gets a heavy 25% because transceiver pricing resets and a 5x run leave the stock exposed to any single soft print. Base 45% for the constructive AI-optical ramp. Bull 15% for the CPO/1.6T acceleration. Cross-check 20% anchors intrinsic value against the peer multiple.</t>
+          <t>Bear gets a heavy 25% because transceiver pricing resets and a 5x run leave the stock exposed to any single soft print. Base 45% for the constructive AI-optical ramp. Bull 10% for the CPO/1.6T acceleration. Cross-check 20% anchors intrinsic value against the peer multiple.</t>
         </is>
       </c>
     </row>
